--- a/backend/signal_logs/index_tracker_BANKNIFTY_2026-08-10.xlsx
+++ b/backend/signal_logs/index_tracker_BANKNIFTY_2026-08-10.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z2"/>
+  <dimension ref="A1:Z3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -638,6 +638,90 @@
         </is>
       </c>
       <c r="Z2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>09:07:33</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>57746.45</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>58013</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="F3" t="n">
+        <v>57700</v>
+      </c>
+      <c r="G3" t="n">
+        <v>164460</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>207990</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>3607680</v>
+      </c>
+      <c r="N3" t="n">
+        <v>4346730</v>
+      </c>
+      <c r="O3" t="n">
+        <v>58000</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1660020</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>58000</v>
+      </c>
+      <c r="R3" t="n">
+        <v>2295450</v>
+      </c>
+      <c r="S3" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="T3" t="n">
+        <v>12.16</v>
+      </c>
+      <c r="U3" t="n">
+        <v>58000</v>
+      </c>
+      <c r="V3" t="n">
+        <v>58000</v>
+      </c>
+      <c r="W3" t="n">
+        <v>58000</v>
+      </c>
+      <c r="X3" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/index_tracker_BANKNIFTY_2026-08-10.xlsx
+++ b/backend/signal_logs/index_tracker_BANKNIFTY_2026-08-10.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z3"/>
+  <dimension ref="A1:Z4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -722,6 +722,96 @@
         </is>
       </c>
       <c r="Z3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>09:10:26</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>57812.3</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="D4" t="n">
+        <v>58013</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.8139999999999999</v>
+      </c>
+      <c r="F4" t="n">
+        <v>57800</v>
+      </c>
+      <c r="G4" t="n">
+        <v>173520</v>
+      </c>
+      <c r="H4" t="n">
+        <v>9060</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>307560</v>
+      </c>
+      <c r="K4" t="n">
+        <v>99570</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>3530580</v>
+      </c>
+      <c r="N4" t="n">
+        <v>4335810</v>
+      </c>
+      <c r="O4" t="n">
+        <v>58000</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1660020</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>58000</v>
+      </c>
+      <c r="R4" t="n">
+        <v>2295450</v>
+      </c>
+      <c r="S4" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="T4" t="n">
+        <v>12.16</v>
+      </c>
+      <c r="U4" t="n">
+        <v>58000</v>
+      </c>
+      <c r="V4" t="n">
+        <v>58000</v>
+      </c>
+      <c r="W4" t="n">
+        <v>58000</v>
+      </c>
+      <c r="X4" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/index_tracker_BANKNIFTY_2026-08-10.xlsx
+++ b/backend/signal_logs/index_tracker_BANKNIFTY_2026-08-10.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z4"/>
+  <dimension ref="A1:Z5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -812,6 +812,96 @@
         </is>
       </c>
       <c r="Z4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>09:12:59</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>57812.3</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="D5" t="n">
+        <v>58013</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.8139999999999999</v>
+      </c>
+      <c r="F5" t="n">
+        <v>57800</v>
+      </c>
+      <c r="G5" t="n">
+        <v>173520</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>307560</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>3530580</v>
+      </c>
+      <c r="N5" t="n">
+        <v>4335810</v>
+      </c>
+      <c r="O5" t="n">
+        <v>58000</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1660020</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>58000</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2295450</v>
+      </c>
+      <c r="S5" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="T5" t="n">
+        <v>12.16</v>
+      </c>
+      <c r="U5" t="n">
+        <v>58000</v>
+      </c>
+      <c r="V5" t="n">
+        <v>58000</v>
+      </c>
+      <c r="W5" t="n">
+        <v>58000</v>
+      </c>
+      <c r="X5" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/index_tracker_BANKNIFTY_2026-08-10.xlsx
+++ b/backend/signal_logs/index_tracker_BANKNIFTY_2026-08-10.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z5"/>
+  <dimension ref="A1:Z6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -902,6 +902,96 @@
         </is>
       </c>
       <c r="Z5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>09:15:54</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>57953.7</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="D6" t="n">
+        <v>58066.6</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.712</v>
+      </c>
+      <c r="F6" t="n">
+        <v>58000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1660020</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1486500</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>2295450</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1987890</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>3635370</v>
+      </c>
+      <c r="N6" t="n">
+        <v>5106660</v>
+      </c>
+      <c r="O6" t="n">
+        <v>58000</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1660020</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>58000</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2295450</v>
+      </c>
+      <c r="S6" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="T6" t="n">
+        <v>12.16</v>
+      </c>
+      <c r="U6" t="n">
+        <v>58000</v>
+      </c>
+      <c r="V6" t="n">
+        <v>58000</v>
+      </c>
+      <c r="W6" t="n">
+        <v>58000</v>
+      </c>
+      <c r="X6" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/index_tracker_BANKNIFTY_2026-08-10.xlsx
+++ b/backend/signal_logs/index_tracker_BANKNIFTY_2026-08-10.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z6"/>
+  <dimension ref="A1:Z7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -992,6 +992,96 @@
         </is>
       </c>
       <c r="Z6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>09:19:03</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>57907.95</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="D7" t="n">
+        <v>58030</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.737</v>
+      </c>
+      <c r="F7" t="n">
+        <v>57900</v>
+      </c>
+      <c r="G7" t="n">
+        <v>160560</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-1499460</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>216600</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-2078850</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>3783180</v>
+      </c>
+      <c r="N7" t="n">
+        <v>5130090</v>
+      </c>
+      <c r="O7" t="n">
+        <v>58000</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1690380</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>58000</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2311620</v>
+      </c>
+      <c r="S7" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="T7" t="n">
+        <v>12.87</v>
+      </c>
+      <c r="U7" t="n">
+        <v>58000</v>
+      </c>
+      <c r="V7" t="n">
+        <v>58000</v>
+      </c>
+      <c r="W7" t="n">
+        <v>58000</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/index_tracker_BANKNIFTY_2026-08-10.xlsx
+++ b/backend/signal_logs/index_tracker_BANKNIFTY_2026-08-10.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z7"/>
+  <dimension ref="A1:Z8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1082,6 +1082,96 @@
         </is>
       </c>
       <c r="Z7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>09:22:04</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>57905.1</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="D8" t="n">
+        <v>58027</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.746</v>
+      </c>
+      <c r="F8" t="n">
+        <v>57900</v>
+      </c>
+      <c r="G8" t="n">
+        <v>174870</v>
+      </c>
+      <c r="H8" t="n">
+        <v>14310</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>227550</v>
+      </c>
+      <c r="K8" t="n">
+        <v>10950</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>3839340</v>
+      </c>
+      <c r="N8" t="n">
+        <v>5148240</v>
+      </c>
+      <c r="O8" t="n">
+        <v>58000</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1699590</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>58000</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2315010</v>
+      </c>
+      <c r="S8" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="T8" t="n">
+        <v>12.78</v>
+      </c>
+      <c r="U8" t="n">
+        <v>58000</v>
+      </c>
+      <c r="V8" t="n">
+        <v>58000</v>
+      </c>
+      <c r="W8" t="n">
+        <v>58000</v>
+      </c>
+      <c r="X8" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/index_tracker_BANKNIFTY_2026-08-10.xlsx
+++ b/backend/signal_logs/index_tracker_BANKNIFTY_2026-08-10.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z8"/>
+  <dimension ref="A1:Z9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1172,6 +1172,96 @@
         </is>
       </c>
       <c r="Z8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>09:25:00</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>57806.5</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="D9" t="n">
+        <v>57960</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.834</v>
+      </c>
+      <c r="F9" t="n">
+        <v>57800</v>
+      </c>
+      <c r="G9" t="n">
+        <v>199500</v>
+      </c>
+      <c r="H9" t="n">
+        <v>24630</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>331080</v>
+      </c>
+      <c r="K9" t="n">
+        <v>103530</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>3739380</v>
+      </c>
+      <c r="N9" t="n">
+        <v>4486230</v>
+      </c>
+      <c r="O9" t="n">
+        <v>58000</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1715580</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>58000</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2318700</v>
+      </c>
+      <c r="S9" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="U9" t="n">
+        <v>58000</v>
+      </c>
+      <c r="V9" t="n">
+        <v>58000</v>
+      </c>
+      <c r="W9" t="n">
+        <v>58000</v>
+      </c>
+      <c r="X9" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/index_tracker_BANKNIFTY_2026-08-10.xlsx
+++ b/backend/signal_logs/index_tracker_BANKNIFTY_2026-08-10.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z9"/>
+  <dimension ref="A1:Z10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1262,6 +1262,96 @@
         </is>
       </c>
       <c r="Z9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>09:28:00</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>57751.7</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D10" t="n">
+        <v>57910.2</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.848</v>
+      </c>
+      <c r="F10" t="n">
+        <v>57800</v>
+      </c>
+      <c r="G10" t="n">
+        <v>210300</v>
+      </c>
+      <c r="H10" t="n">
+        <v>10800</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>336630</v>
+      </c>
+      <c r="K10" t="n">
+        <v>5550</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>3837900</v>
+      </c>
+      <c r="N10" t="n">
+        <v>4526460</v>
+      </c>
+      <c r="O10" t="n">
+        <v>58000</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1709250</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>58000</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2320620</v>
+      </c>
+      <c r="S10" t="n">
+        <v>14</v>
+      </c>
+      <c r="T10" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="U10" t="n">
+        <v>58000</v>
+      </c>
+      <c r="V10" t="n">
+        <v>58000</v>
+      </c>
+      <c r="W10" t="n">
+        <v>58000</v>
+      </c>
+      <c r="X10" t="n">
+        <v>-0.43</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/index_tracker_BANKNIFTY_2026-08-10.xlsx
+++ b/backend/signal_logs/index_tracker_BANKNIFTY_2026-08-10.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z10"/>
+  <dimension ref="A1:Z11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1352,6 +1352,96 @@
         </is>
       </c>
       <c r="Z10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>09:30:42</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>57702.35</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>57911</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="F11" t="n">
+        <v>57700</v>
+      </c>
+      <c r="G11" t="n">
+        <v>197280</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-13020</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>216840</v>
+      </c>
+      <c r="K11" t="n">
+        <v>-119790</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>3818190</v>
+      </c>
+      <c r="N11" t="n">
+        <v>4583850</v>
+      </c>
+      <c r="O11" t="n">
+        <v>58000</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1703730</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>58000</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2338230</v>
+      </c>
+      <c r="S11" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>12.83</v>
+      </c>
+      <c r="U11" t="n">
+        <v>58000</v>
+      </c>
+      <c r="V11" t="n">
+        <v>58000</v>
+      </c>
+      <c r="W11" t="n">
+        <v>58000</v>
+      </c>
+      <c r="X11" t="n">
+        <v>-0.51</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/index_tracker_BANKNIFTY_2026-08-10.xlsx
+++ b/backend/signal_logs/index_tracker_BANKNIFTY_2026-08-10.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z11"/>
+  <dimension ref="A1:Z12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1442,6 +1442,96 @@
         </is>
       </c>
       <c r="Z11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>09:33:34</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>57643.4</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="D12" t="n">
+        <v>57837.4</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.921</v>
+      </c>
+      <c r="F12" t="n">
+        <v>57600</v>
+      </c>
+      <c r="G12" t="n">
+        <v>136110</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-61170</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>132750</v>
+      </c>
+      <c r="K12" t="n">
+        <v>-84090</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>4706250</v>
+      </c>
+      <c r="N12" t="n">
+        <v>5111250</v>
+      </c>
+      <c r="O12" t="n">
+        <v>58000</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1699080</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>58000</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2342040</v>
+      </c>
+      <c r="S12" t="n">
+        <v>14</v>
+      </c>
+      <c r="T12" t="n">
+        <v>12.79</v>
+      </c>
+      <c r="U12" t="n">
+        <v>58000</v>
+      </c>
+      <c r="V12" t="n">
+        <v>58000</v>
+      </c>
+      <c r="W12" t="n">
+        <v>57900</v>
+      </c>
+      <c r="X12" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/index_tracker_BANKNIFTY_2026-08-10.xlsx
+++ b/backend/signal_logs/index_tracker_BANKNIFTY_2026-08-10.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z12"/>
+  <dimension ref="A1:Z13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1532,6 +1532,96 @@
         </is>
       </c>
       <c r="Z12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>09:36:21</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>57578.8</v>
+      </c>
+      <c r="C13" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="D13" t="n">
+        <v>57788</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F13" t="n">
+        <v>57600</v>
+      </c>
+      <c r="G13" t="n">
+        <v>143190</v>
+      </c>
+      <c r="H13" t="n">
+        <v>7080</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>145620</v>
+      </c>
+      <c r="K13" t="n">
+        <v>12870</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
+        <v>4687020</v>
+      </c>
+      <c r="N13" t="n">
+        <v>5207880</v>
+      </c>
+      <c r="O13" t="n">
+        <v>58000</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1700700</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>58000</v>
+      </c>
+      <c r="R13" t="n">
+        <v>2370090</v>
+      </c>
+      <c r="S13" t="n">
+        <v>14</v>
+      </c>
+      <c r="T13" t="n">
+        <v>12.74</v>
+      </c>
+      <c r="U13" t="n">
+        <v>58000</v>
+      </c>
+      <c r="V13" t="n">
+        <v>58000</v>
+      </c>
+      <c r="W13" t="n">
+        <v>57900</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/index_tracker_BANKNIFTY_2026-08-10.xlsx
+++ b/backend/signal_logs/index_tracker_BANKNIFTY_2026-08-10.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z13"/>
+  <dimension ref="A1:Z14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1622,6 +1622,96 @@
         </is>
       </c>
       <c r="Z13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>09:39:09</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>57592.3</v>
+      </c>
+      <c r="C14" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="D14" t="n">
+        <v>57800</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.887</v>
+      </c>
+      <c r="F14" t="n">
+        <v>57600</v>
+      </c>
+      <c r="G14" t="n">
+        <v>152910</v>
+      </c>
+      <c r="H14" t="n">
+        <v>9720</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>159690</v>
+      </c>
+      <c r="K14" t="n">
+        <v>14070</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
+        <v>4701870</v>
+      </c>
+      <c r="N14" t="n">
+        <v>5302560</v>
+      </c>
+      <c r="O14" t="n">
+        <v>58000</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1699080</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>58000</v>
+      </c>
+      <c r="R14" t="n">
+        <v>2404590</v>
+      </c>
+      <c r="S14" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="T14" t="n">
+        <v>12.73</v>
+      </c>
+      <c r="U14" t="n">
+        <v>58000</v>
+      </c>
+      <c r="V14" t="n">
+        <v>58000</v>
+      </c>
+      <c r="W14" t="n">
+        <v>57900</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-0.53</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/index_tracker_BANKNIFTY_2026-08-10.xlsx
+++ b/backend/signal_logs/index_tracker_BANKNIFTY_2026-08-10.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z14"/>
+  <dimension ref="A1:Z15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1712,6 +1712,96 @@
         </is>
       </c>
       <c r="Z14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>09:42:13</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>57604.9</v>
+      </c>
+      <c r="C15" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="D15" t="n">
+        <v>57800.2</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.887</v>
+      </c>
+      <c r="F15" t="n">
+        <v>57600</v>
+      </c>
+      <c r="G15" t="n">
+        <v>167250</v>
+      </c>
+      <c r="H15" t="n">
+        <v>14340</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>180240</v>
+      </c>
+      <c r="K15" t="n">
+        <v>20550</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>4736580</v>
+      </c>
+      <c r="N15" t="n">
+        <v>5338710</v>
+      </c>
+      <c r="O15" t="n">
+        <v>58000</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1699260</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>58000</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2408820</v>
+      </c>
+      <c r="S15" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="T15" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="U15" t="n">
+        <v>58000</v>
+      </c>
+      <c r="V15" t="n">
+        <v>58000</v>
+      </c>
+      <c r="W15" t="n">
+        <v>57800</v>
+      </c>
+      <c r="X15" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/index_tracker_BANKNIFTY_2026-08-10.xlsx
+++ b/backend/signal_logs/index_tracker_BANKNIFTY_2026-08-10.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z15"/>
+  <dimension ref="A1:Z16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1802,6 +1802,96 @@
         </is>
       </c>
       <c r="Z15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>09:44:52</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>57628.65</v>
+      </c>
+      <c r="C16" t="n">
+        <v>-0.24</v>
+      </c>
+      <c r="D16" t="n">
+        <v>57820</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.888</v>
+      </c>
+      <c r="F16" t="n">
+        <v>57600</v>
+      </c>
+      <c r="G16" t="n">
+        <v>181170</v>
+      </c>
+      <c r="H16" t="n">
+        <v>13920</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>196830</v>
+      </c>
+      <c r="K16" t="n">
+        <v>16590</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M16" t="n">
+        <v>4773450</v>
+      </c>
+      <c r="N16" t="n">
+        <v>5377380</v>
+      </c>
+      <c r="O16" t="n">
+        <v>58000</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1699410</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>58000</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2411430</v>
+      </c>
+      <c r="S16" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="T16" t="n">
+        <v>12.71</v>
+      </c>
+      <c r="U16" t="n">
+        <v>58000</v>
+      </c>
+      <c r="V16" t="n">
+        <v>58000</v>
+      </c>
+      <c r="W16" t="n">
+        <v>57800</v>
+      </c>
+      <c r="X16" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/index_tracker_BANKNIFTY_2026-08-10.xlsx
+++ b/backend/signal_logs/index_tracker_BANKNIFTY_2026-08-10.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z16"/>
+  <dimension ref="A1:Z17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1892,6 +1892,96 @@
         </is>
       </c>
       <c r="Z16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>09:47:37</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>57647.75</v>
+      </c>
+      <c r="C17" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="D17" t="n">
+        <v>57812.2</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.888</v>
+      </c>
+      <c r="F17" t="n">
+        <v>57600</v>
+      </c>
+      <c r="G17" t="n">
+        <v>194460</v>
+      </c>
+      <c r="H17" t="n">
+        <v>13290</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>204990</v>
+      </c>
+      <c r="K17" t="n">
+        <v>8160</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>4805250</v>
+      </c>
+      <c r="N17" t="n">
+        <v>5410080</v>
+      </c>
+      <c r="O17" t="n">
+        <v>58000</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1700100</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>58000</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2412480</v>
+      </c>
+      <c r="S17" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="T17" t="n">
+        <v>12.71</v>
+      </c>
+      <c r="U17" t="n">
+        <v>58000</v>
+      </c>
+      <c r="V17" t="n">
+        <v>58000</v>
+      </c>
+      <c r="W17" t="n">
+        <v>57800</v>
+      </c>
+      <c r="X17" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/index_tracker_BANKNIFTY_2026-08-10.xlsx
+++ b/backend/signal_logs/index_tracker_BANKNIFTY_2026-08-10.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z17"/>
+  <dimension ref="A1:Z18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1982,6 +1982,96 @@
         </is>
       </c>
       <c r="Z17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>09:50:23</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>57615.7</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="D18" t="n">
+        <v>57800</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="F18" t="n">
+        <v>57600</v>
+      </c>
+      <c r="G18" t="n">
+        <v>197490</v>
+      </c>
+      <c r="H18" t="n">
+        <v>3030</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>201390</v>
+      </c>
+      <c r="K18" t="n">
+        <v>-3600</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
+        <v>4816980</v>
+      </c>
+      <c r="N18" t="n">
+        <v>5410350</v>
+      </c>
+      <c r="O18" t="n">
+        <v>58000</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1701690</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>58000</v>
+      </c>
+      <c r="R18" t="n">
+        <v>2413950</v>
+      </c>
+      <c r="S18" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="T18" t="n">
+        <v>12.71</v>
+      </c>
+      <c r="U18" t="n">
+        <v>58000</v>
+      </c>
+      <c r="V18" t="n">
+        <v>58000</v>
+      </c>
+      <c r="W18" t="n">
+        <v>57800</v>
+      </c>
+      <c r="X18" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/index_tracker_BANKNIFTY_2026-08-10.xlsx
+++ b/backend/signal_logs/index_tracker_BANKNIFTY_2026-08-10.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z18"/>
+  <dimension ref="A1:Z19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2072,6 +2072,96 @@
         </is>
       </c>
       <c r="Z18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>09:53:18</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>57589.4</v>
+      </c>
+      <c r="C19" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="D19" t="n">
+        <v>57787.2</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.892</v>
+      </c>
+      <c r="F19" t="n">
+        <v>57600</v>
+      </c>
+      <c r="G19" t="n">
+        <v>199110</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1620</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>199620</v>
+      </c>
+      <c r="K19" t="n">
+        <v>-1770</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="M19" t="n">
+        <v>4845810</v>
+      </c>
+      <c r="N19" t="n">
+        <v>5429940</v>
+      </c>
+      <c r="O19" t="n">
+        <v>58000</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1700190</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>58000</v>
+      </c>
+      <c r="R19" t="n">
+        <v>2419620</v>
+      </c>
+      <c r="S19" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="T19" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="U19" t="n">
+        <v>58000</v>
+      </c>
+      <c r="V19" t="n">
+        <v>58000</v>
+      </c>
+      <c r="W19" t="n">
+        <v>57800</v>
+      </c>
+      <c r="X19" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/index_tracker_BANKNIFTY_2026-08-10.xlsx
+++ b/backend/signal_logs/index_tracker_BANKNIFTY_2026-08-10.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z19"/>
+  <dimension ref="A1:Z20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2162,6 +2162,96 @@
         </is>
       </c>
       <c r="Z19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>09:56:23</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>57569.9</v>
+      </c>
+      <c r="C20" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="D20" t="n">
+        <v>57787</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.884</v>
+      </c>
+      <c r="F20" t="n">
+        <v>57600</v>
+      </c>
+      <c r="G20" t="n">
+        <v>196320</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-2790</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>212010</v>
+      </c>
+      <c r="K20" t="n">
+        <v>12390</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M20" t="n">
+        <v>4845090</v>
+      </c>
+      <c r="N20" t="n">
+        <v>5479470</v>
+      </c>
+      <c r="O20" t="n">
+        <v>58000</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1699170</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>58000</v>
+      </c>
+      <c r="R20" t="n">
+        <v>2445240</v>
+      </c>
+      <c r="S20" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="T20" t="n">
+        <v>12.66</v>
+      </c>
+      <c r="U20" t="n">
+        <v>58000</v>
+      </c>
+      <c r="V20" t="n">
+        <v>58000</v>
+      </c>
+      <c r="W20" t="n">
+        <v>57800</v>
+      </c>
+      <c r="X20" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/index_tracker_BANKNIFTY_2026-08-10.xlsx
+++ b/backend/signal_logs/index_tracker_BANKNIFTY_2026-08-10.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z20"/>
+  <dimension ref="A1:Z21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2252,6 +2252,96 @@
         </is>
       </c>
       <c r="Z20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>09:59:01</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>57564.4</v>
+      </c>
+      <c r="C21" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="D21" t="n">
+        <v>57763.2</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.881</v>
+      </c>
+      <c r="F21" t="n">
+        <v>57600</v>
+      </c>
+      <c r="G21" t="n">
+        <v>193320</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-3000</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>213600</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1590</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M21" t="n">
+        <v>4851060</v>
+      </c>
+      <c r="N21" t="n">
+        <v>5506950</v>
+      </c>
+      <c r="O21" t="n">
+        <v>58000</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1700790</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>58000</v>
+      </c>
+      <c r="R21" t="n">
+        <v>2461770</v>
+      </c>
+      <c r="S21" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="T21" t="n">
+        <v>12.68</v>
+      </c>
+      <c r="U21" t="n">
+        <v>58000</v>
+      </c>
+      <c r="V21" t="n">
+        <v>58000</v>
+      </c>
+      <c r="W21" t="n">
+        <v>57800</v>
+      </c>
+      <c r="X21" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/index_tracker_BANKNIFTY_2026-08-10.xlsx
+++ b/backend/signal_logs/index_tracker_BANKNIFTY_2026-08-10.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z21"/>
+  <dimension ref="A1:Z22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2342,6 +2342,96 @@
         </is>
       </c>
       <c r="Z21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>10:01:46</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>57607.4</v>
+      </c>
+      <c r="C22" t="n">
+        <v>-0.24</v>
+      </c>
+      <c r="D22" t="n">
+        <v>57794</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.878</v>
+      </c>
+      <c r="F22" t="n">
+        <v>57600</v>
+      </c>
+      <c r="G22" t="n">
+        <v>194580</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1260</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>220890</v>
+      </c>
+      <c r="K22" t="n">
+        <v>7290</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M22" t="n">
+        <v>4857210</v>
+      </c>
+      <c r="N22" t="n">
+        <v>5530140</v>
+      </c>
+      <c r="O22" t="n">
+        <v>58000</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1700670</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>58000</v>
+      </c>
+      <c r="R22" t="n">
+        <v>2462940</v>
+      </c>
+      <c r="S22" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="T22" t="n">
+        <v>12.64</v>
+      </c>
+      <c r="U22" t="n">
+        <v>58000</v>
+      </c>
+      <c r="V22" t="n">
+        <v>58000</v>
+      </c>
+      <c r="W22" t="n">
+        <v>57800</v>
+      </c>
+      <c r="X22" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/index_tracker_BANKNIFTY_2026-08-10.xlsx
+++ b/backend/signal_logs/index_tracker_BANKNIFTY_2026-08-10.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z22"/>
+  <dimension ref="A1:Z23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2432,6 +2432,96 @@
         </is>
       </c>
       <c r="Z22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>10:04:31</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>57640.25</v>
+      </c>
+      <c r="C23" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="D23" t="n">
+        <v>57820</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="F23" t="n">
+        <v>57600</v>
+      </c>
+      <c r="G23" t="n">
+        <v>194910</v>
+      </c>
+      <c r="H23" t="n">
+        <v>330</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>218640</v>
+      </c>
+      <c r="K23" t="n">
+        <v>-2250</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="M23" t="n">
+        <v>4850850</v>
+      </c>
+      <c r="N23" t="n">
+        <v>5514870</v>
+      </c>
+      <c r="O23" t="n">
+        <v>58000</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1698660</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>58000</v>
+      </c>
+      <c r="R23" t="n">
+        <v>2456880</v>
+      </c>
+      <c r="S23" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="T23" t="n">
+        <v>12.65</v>
+      </c>
+      <c r="U23" t="n">
+        <v>58000</v>
+      </c>
+      <c r="V23" t="n">
+        <v>58000</v>
+      </c>
+      <c r="W23" t="n">
+        <v>57800</v>
+      </c>
+      <c r="X23" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/index_tracker_BANKNIFTY_2026-08-10.xlsx
+++ b/backend/signal_logs/index_tracker_BANKNIFTY_2026-08-10.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z23"/>
+  <dimension ref="A1:Z24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2522,6 +2522,96 @@
         </is>
       </c>
       <c r="Z23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>10:07:20</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>57635.8</v>
+      </c>
+      <c r="C24" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="D24" t="n">
+        <v>57829</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.881</v>
+      </c>
+      <c r="F24" t="n">
+        <v>57600</v>
+      </c>
+      <c r="G24" t="n">
+        <v>199140</v>
+      </c>
+      <c r="H24" t="n">
+        <v>4230</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>222720</v>
+      </c>
+      <c r="K24" t="n">
+        <v>4080</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M24" t="n">
+        <v>4870590</v>
+      </c>
+      <c r="N24" t="n">
+        <v>5528100</v>
+      </c>
+      <c r="O24" t="n">
+        <v>58000</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1701000</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>58000</v>
+      </c>
+      <c r="R24" t="n">
+        <v>2458380</v>
+      </c>
+      <c r="S24" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="T24" t="n">
+        <v>12.65</v>
+      </c>
+      <c r="U24" t="n">
+        <v>58000</v>
+      </c>
+      <c r="V24" t="n">
+        <v>58000</v>
+      </c>
+      <c r="W24" t="n">
+        <v>57800</v>
+      </c>
+      <c r="X24" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/index_tracker_BANKNIFTY_2026-08-10.xlsx
+++ b/backend/signal_logs/index_tracker_BANKNIFTY_2026-08-10.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z24"/>
+  <dimension ref="A1:Z25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2612,6 +2612,96 @@
         </is>
       </c>
       <c r="Z24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>10:10:03</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>57585</v>
+      </c>
+      <c r="C25" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="D25" t="n">
+        <v>57800</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.879</v>
+      </c>
+      <c r="F25" t="n">
+        <v>57600</v>
+      </c>
+      <c r="G25" t="n">
+        <v>199080</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-60</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>224610</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1890</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M25" t="n">
+        <v>4869780</v>
+      </c>
+      <c r="N25" t="n">
+        <v>5538210</v>
+      </c>
+      <c r="O25" t="n">
+        <v>58000</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1702050</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>58000</v>
+      </c>
+      <c r="R25" t="n">
+        <v>2459820</v>
+      </c>
+      <c r="S25" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="T25" t="n">
+        <v>12.66</v>
+      </c>
+      <c r="U25" t="n">
+        <v>58000</v>
+      </c>
+      <c r="V25" t="n">
+        <v>58000</v>
+      </c>
+      <c r="W25" t="n">
+        <v>57800</v>
+      </c>
+      <c r="X25" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/index_tracker_BANKNIFTY_2026-08-10.xlsx
+++ b/backend/signal_logs/index_tracker_BANKNIFTY_2026-08-10.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z25"/>
+  <dimension ref="A1:Z26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2702,6 +2702,96 @@
         </is>
       </c>
       <c r="Z25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>10:12:53</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>57598.35</v>
+      </c>
+      <c r="C26" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="D26" t="n">
+        <v>57790</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.879</v>
+      </c>
+      <c r="F26" t="n">
+        <v>57600</v>
+      </c>
+      <c r="G26" t="n">
+        <v>202020</v>
+      </c>
+      <c r="H26" t="n">
+        <v>2940</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>228060</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3450</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M26" t="n">
+        <v>4879980</v>
+      </c>
+      <c r="N26" t="n">
+        <v>5551890</v>
+      </c>
+      <c r="O26" t="n">
+        <v>58000</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1702680</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>58000</v>
+      </c>
+      <c r="R26" t="n">
+        <v>2462460</v>
+      </c>
+      <c r="S26" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="T26" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="U26" t="n">
+        <v>58000</v>
+      </c>
+      <c r="V26" t="n">
+        <v>58000</v>
+      </c>
+      <c r="W26" t="n">
+        <v>57800</v>
+      </c>
+      <c r="X26" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/index_tracker_BANKNIFTY_2026-08-10.xlsx
+++ b/backend/signal_logs/index_tracker_BANKNIFTY_2026-08-10.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z26"/>
+  <dimension ref="A1:Z27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2792,6 +2792,96 @@
         </is>
       </c>
       <c r="Z26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>10:15:36</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>57636.55</v>
+      </c>
+      <c r="C27" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="D27" t="n">
+        <v>57835</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.879</v>
+      </c>
+      <c r="F27" t="n">
+        <v>57600</v>
+      </c>
+      <c r="G27" t="n">
+        <v>208140</v>
+      </c>
+      <c r="H27" t="n">
+        <v>6120</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>229140</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1080</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M27" t="n">
+        <v>4880070</v>
+      </c>
+      <c r="N27" t="n">
+        <v>5552790</v>
+      </c>
+      <c r="O27" t="n">
+        <v>58000</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1701570</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>58000</v>
+      </c>
+      <c r="R27" t="n">
+        <v>2462940</v>
+      </c>
+      <c r="S27" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="T27" t="n">
+        <v>12.65</v>
+      </c>
+      <c r="U27" t="n">
+        <v>58000</v>
+      </c>
+      <c r="V27" t="n">
+        <v>58000</v>
+      </c>
+      <c r="W27" t="n">
+        <v>57800</v>
+      </c>
+      <c r="X27" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/index_tracker_BANKNIFTY_2026-08-10.xlsx
+++ b/backend/signal_logs/index_tracker_BANKNIFTY_2026-08-10.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z27"/>
+  <dimension ref="A1:Z28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2882,6 +2882,96 @@
         </is>
       </c>
       <c r="Z27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>10:18:46</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>57693.1</v>
+      </c>
+      <c r="C28" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="D28" t="n">
+        <v>57850</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.785</v>
+      </c>
+      <c r="F28" t="n">
+        <v>57700</v>
+      </c>
+      <c r="G28" t="n">
+        <v>246270</v>
+      </c>
+      <c r="H28" t="n">
+        <v>38130</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>272940</v>
+      </c>
+      <c r="K28" t="n">
+        <v>43800</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M28" t="n">
+        <v>3969510</v>
+      </c>
+      <c r="N28" t="n">
+        <v>5056260</v>
+      </c>
+      <c r="O28" t="n">
+        <v>58000</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1699710</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>58000</v>
+      </c>
+      <c r="R28" t="n">
+        <v>2457240</v>
+      </c>
+      <c r="S28" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="T28" t="n">
+        <v>12.65</v>
+      </c>
+      <c r="U28" t="n">
+        <v>58000</v>
+      </c>
+      <c r="V28" t="n">
+        <v>58000</v>
+      </c>
+      <c r="W28" t="n">
+        <v>58000</v>
+      </c>
+      <c r="X28" t="n">
+        <v>-0.53</v>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
